--- a/examples/hello-table/fixtures/finance.libreoffice-resaved.xlsx
+++ b/examples/hello-table/fixtures/finance.libreoffice-resaved.xlsx
@@ -11,11 +11,11 @@
     <sheet name="Q3" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="ox_3f1c2a90_0000_4c1e_9a00_000000000011" vbProcedure="false">Q3!$A$1</definedName>
-    <definedName function="false" hidden="false" name="ox_3f1c2a90_0000_4c1e_9a00_000000000012" vbProcedure="false">Q3!$A$1:$B$4</definedName>
-    <definedName function="false" hidden="false" name="ox_3f1c2a90_0000_4c1e_9a00_000000000013" vbProcedure="false">Q3!$B$5</definedName>
-    <definedName function="false" hidden="false" name="ox_revision" vbProcedure="false">"3b0b95b52b828de91bcdb13f"</definedName>
-    <definedName function="false" hidden="false" name="ox_workbook" vbProcedure="false">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
+    <definedName function="false" hidden="false" name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000011" vbProcedure="false">Q3!$A$1</definedName>
+    <definedName function="false" hidden="false" name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000012" vbProcedure="false">Q3!$A$1:$B$4</definedName>
+    <definedName function="false" hidden="false" name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000013" vbProcedure="false">Q3!$B$5</definedName>
+    <definedName function="false" hidden="false" name="mleaf_revision" vbProcedure="false">"3b0b95b52b828de91bcdb13f"</definedName>
+    <definedName function="false" hidden="false" name="mleaf_workbook" vbProcedure="false">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>

--- a/examples/hello-table/fixtures/finance.libreoffice-resaved.xlsx
+++ b/examples/hello-table/fixtures/finance.libreoffice-resaved.xlsx
@@ -14,7 +14,7 @@
     <definedName function="false" hidden="false" name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000011" vbProcedure="false">Q3!$A$1</definedName>
     <definedName function="false" hidden="false" name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000012" vbProcedure="false">Q3!$A$1:$B$4</definedName>
     <definedName function="false" hidden="false" name="mleaf_3f1c2a90_0000_4c1e_9a00_000000000013" vbProcedure="false">Q3!$B$5</definedName>
-    <definedName function="false" hidden="false" name="mleaf_revision" vbProcedure="false">"3b0b95b52b828de91bcdb13f"</definedName>
+    <definedName function="false" hidden="false" name="mleaf_revision" vbProcedure="false">"c50ea0fe36a3631b2dbab632"</definedName>
     <definedName function="false" hidden="false" name="mleaf_workbook" vbProcedure="false">"3f1c2a90-0000-4c1e-9a00-000000000010"</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -261,6 +261,10 @@
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.71"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
